--- a/data/trans_orig/P79A5_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P79A5_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tiene resuelto el retraso en los pagos de los impuestos relacionados con vehículos en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si tiene resuelto el retraso en los pagos de los impuestos relacionados con vehículos, IBI, etc en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1849</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2361</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>4210</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>76,55%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1411</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>951</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>705</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>705</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>75,68%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,27 +1411,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7018</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>4233</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8590</t>
+          <t>8857</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1481,27 +1481,27 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9344</t>
+          <t>9770</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6323</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10916</t>
+          <t>11428</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4778</t>
+          <t>4624</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1604,12 +1604,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4593</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>44,31%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8590</t>
+          <t>8857</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8590</t>
+          <t>8857</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8590</t>
+          <t>8857</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>10916</t>
+          <t>11428</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10916</t>
+          <t>11428</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10916</t>
+          <t>11428</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14097</t>
+          <t>15163</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9890</t>
+          <t>11341</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16159</t>
+          <t>17169</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,27 +1789,27 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>4263</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7975</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>20812</t>
+          <t>22128</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16433</t>
+          <t>17645</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23340</t>
+          <t>24621</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2537</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>522</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>6350</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8177</t>
+          <t>8363</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16634</t>
+          <t>17691</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16634</t>
+          <t>17691</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16634</t>
+          <t>17691</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7975</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7975</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7975</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>24610</t>
+          <t>26008</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>24610</t>
+          <t>26008</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>24610</t>
+          <t>26008</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>3454</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>9938</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9598</t>
+          <t>11923</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12097</t>
+          <t>14573</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>16200</t>
+          <t>19030</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11715</t>
+          <t>13863</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19838</t>
+          <t>22964</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,08%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3347</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>7584</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>4682</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1641</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>8059</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>7487</t>
+          <t>8612</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>4678</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11972</t>
+          <t>13779</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>49,85%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>13738</t>
+          <t>16605</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13738</t>
+          <t>16605</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13738</t>
+          <t>16605</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>23687</t>
+          <t>27642</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>23687</t>
+          <t>27642</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23687</t>
+          <t>27642</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2475,27 +2475,27 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7641</t>
+          <t>8549</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3948</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>10728</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2510,27 +2510,27 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>9711</t>
+          <t>10990</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>6726</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11991</t>
+          <t>13169</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5973</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6724</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>48,92%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>10728</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>10728</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>10728</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>11991</t>
+          <t>13169</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>11991</t>
+          <t>13169</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11991</t>
+          <t>13169</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>33181</t>
+          <t>35592</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26885</t>
+          <t>28725</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37544</t>
+          <t>40048</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>29826</t>
+          <t>33779</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24390</t>
+          <t>27729</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33770</t>
+          <t>37998</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>63007</t>
+          <t>69371</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54442</t>
+          <t>61157</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>68970</t>
+          <t>75988</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,75%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>8627</t>
+          <t>9303</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14923</t>
+          <t>16170</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>5720</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14731</t>
+          <t>15989</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>17922</t>
+          <t>19242</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>11959</t>
+          <t>12625</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>26487</t>
+          <t>27456</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>41808</t>
+          <t>44895</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>41808</t>
+          <t>44895</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>41808</t>
+          <t>44895</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>39121</t>
+          <t>43718</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>39121</t>
+          <t>43718</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>39121</t>
+          <t>43718</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>80929</t>
+          <t>88613</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>80929</t>
+          <t>88613</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>80929</t>
+          <t>88613</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
